--- a/docs/user/tableToSwcArxml/SwcTemplate.xlsx
+++ b/docs/user/tableToSwcArxml/SwcTemplate.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1375,12 +1375,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>目标文件</t>
+          <t>名称校验</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Target ARXML 相对 projectRoot，目标文件和所在包必须已存在；它不是导出路径。最终输出由 outputDir / inPlace / dryRun 控制。</t>
+          <t>新建 Name 和路径各段必须以 ASCII 字母开头，只含字母、数字、下划线，最长 128 字符。枚举 Label 等文本可用中文；Runnable Symbol 使用 C 标识符。自动长名称截断并追加哈希。</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -1391,12 +1391,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>空值与布尔值</t>
+          <t>目标文件</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>布尔留空为 N；接受 Y/N、TRUE/FALSE、YES/NO、1/0（不区分大小写）。其他默认值逐列列出。合法但不生效的配置会 WARNING；非法值仍 ERROR。</t>
+          <t>Target ARXML 相对 projectRoot，目标文件和所在包必须已存在；它不是导出路径。最终输出由 outputDir / inPlace / dryRun 控制。</t>
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -1407,12 +1407,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>错误与写出</t>
+          <t>输出与重定义</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>任一 ERROR 阻止全部 ARXML 写出，退出码 1；WARNING 不阻止写出。空模板不产生对象，运行会提示没有有效记录。</t>
+          <t>outputDir 不能覆盖任何输入 ARXML（包括链接别名），覆盖源文件必须明确使用 inPlace。其他文件已有同路径对象时禁止再次创建；候选文件解析失败也会阻止写出。</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -1423,12 +1423,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>数据表操作</t>
+          <t>空值与布尔值</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>每页使用 Excel 表格：从表格最后一个单元格按 Tab 追加行，筛选会自动扩展。若在表外粘贴，使用“调整表格大小”纳入新行；解析器仍读取整页。</t>
+          <t>布尔留空为 N；接受 Y/N、TRUE/FALSE、YES/NO、1/0（不区分大小写）。其他默认值逐列列出。合法但不生效的配置会 WARNING；非法值仍 ERROR。</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -1439,12 +1439,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>排序与合并</t>
+          <t>错误与写出</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>批量数据优先逐行重复公共字段；合并单元格虽可读取，但不利于 Excel 表格排序/筛选，不建议在数据表中合并。</t>
+          <t>任一 ERROR 阻止全部 ARXML 写出，退出码 1；WARNING 不阻止写出。空模板不产生对象，运行会提示没有有效记录。</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
@@ -1455,12 +1455,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>列移动与下拉</t>
+          <t>数据表操作</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>工具按列名读取；移动整列后应检查 Excel 数据验证范围。下拉、数值验证和批注用于辅助，复制粘贴仍须经工具校验。</t>
+          <t>每页使用 Excel 表格：从表格最后一个单元格按 Tab 追加行，筛选会自动扩展。若在表外粘贴，使用“调整表格大小”纳入新行；解析器仍读取整页。</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -1471,12 +1471,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SR P / SR R</t>
+          <t>排序与合并</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Artifact=Y 时必须指定已有 Runnable Name，且已有对应容器。P：Send（默认）/ Write；R：ReceiveByArgument（默认）/ ReceiveByValue / Read。</t>
+          <t>批量数据优先逐行重复公共字段；合并单元格虽可读取，但不利于 Excel 表格排序/筛选，不建议在数据表中合并。</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -1487,12 +1487,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CS P / CS R</t>
+          <t>列移动与下拉</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CS P：每个 operation 新建 runnable/event；名称留空自动命名，多 operation 给手填名追加后缀。CS R：已有调用方 Runnable Name 必填，每个 operation 创建同步调用点（超时 0.0）。</t>
+          <t>工具按列名读取；移动整列后应检查 Excel 数据验证范围。下拉、数值验证和批注用于辅助，复制粘贴仍须经工具校验。</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -1503,12 +1503,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ComSpec 触发</t>
+          <t>SR P / SR R</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>P：超时非空（含 0）或 E2E=Y。R：Enable Update=Y 或 Queue Length&gt;0，两者互斥。仅填 N 或 Queue Length=0 不触发；新端口为全部数据元素生成。</t>
+          <t>Artifact=Y 时必须指定已有 Runnable Name，且已有对应容器。P：Send（默认）/ Write；R：ReceiveByArgument（默认）/ ReceiveByValue / Read。</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
@@ -1519,12 +1519,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>已知限制</t>
+          <t>CS P / CS R</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>组件及内部行为/访问点容器须按对应功能预先存在；CS 不生成应用错误；SR 接口以外不自动生成数据访问点。无参数 operation 的参数三列全空，不能混用同名有参数声明。</t>
+          <t>CS P：每个 operation 新建 runnable/event；名称留空自动命名，多 operation 给手填名追加后缀。CS R：已有调用方 Runnable Name 必填，每个 operation 创建同步调用点（超时 0.0）。</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -1535,12 +1535,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>兼容名称</t>
+          <t>ComSpec 触发</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Data-Accesses → Data Accesses；SWC → SW-C；Runnable / Runnable Ref → Runnable Name；Receive Mode → Access Kind（Argument / Value 仍兼容）；Base Type Ref → Implementation Data Type Ref。</t>
+          <t>P：超时非空（含 0）或 E2E=Y。R：Enable Update=Y 或 Queue Length&gt;0，两者互斥。仅填 N 或 Queue Length=0 不触发；新端口为全部数据元素生成。</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
@@ -1551,12 +1551,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>其他旧列名</t>
+          <t>已知限制</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Create Access → Create RTE Artifact；Transmission Acknowledge → Transmission Acknowledge Timeout；QueueLength → Queue Length；Data Element / Operation / Argument → 对应的 ... Name。</t>
+          <t>组件及内部行为/访问点容器须按对应功能预先存在；CS 不生成应用错误；SR 接口以外不自动生成数据访问点。无参数 operation 的参数三列全空，不能混用同名有参数声明。</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
@@ -1567,12 +1567,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>精确类型</t>
+          <t>兼容名称</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>枚举底层列引用 IMPLEMENTATION-DATA-TYPE，不是 SW-BASE-TYPE。所有时间间隔/超时单位为秒。</t>
+          <t>Data-Accesses → Data Accesses；SWC → SW-C；Runnable / Runnable Ref → Runnable Name；Receive Mode → Access Kind（Argument / Value 仍兼容）；Base Type Ref → Implementation Data Type Ref。</t>
         </is>
       </c>
       <c r="C21" s="2" t="n"/>
@@ -1583,12 +1583,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>字段导航</t>
+          <t>其他旧列名</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>点击下方工作表标题跳转输入页；字段说明与各页表头批注来自同一份定义。</t>
+          <t>Create Access → Create RTE Artifact；Transmission Acknowledge → Transmission Acknowledge Timeout；QueueLength → Queue Length；Data Element / Operation / Argument → 对应的 ... Name。</t>
         </is>
       </c>
       <c r="C22" s="2" t="n"/>
@@ -1597,290 +1597,258 @@
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>精确类型</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>枚举底层列引用 IMPLEMENTATION-DATA-TYPE，不是 SW-BASE-TYPE。所有时间间隔/超时单位为秒。</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>字段导航</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>点击下方工作表标题跳转输入页；字段说明与各页表头批注来自同一份定义。</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Components</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Components</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>SW-C</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>工作簿内组件标识；在 Components 中定义，不要求等于组件 SHORT-NAME。</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>LIT</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Components</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Component Path</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>清单中已有的软件组件类型路径；本页只建立映射，不新建组件。</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>/BcmSystem/SwComponentTypes/LIT</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Enumerations</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Enumerations</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Type Path</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>新建实现数据类型的完整 AUTOSAR 路径；同路径的成员/枚举行按顺序合并。</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>/Pkg/Types/Mode</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Enumerations</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>整数枚举值；同一类型内不能重复。</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Enumerations</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>枚举值对应文本；同一类型内不能重复。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Mode_Off</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Enumerations</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Implementation Data Type Ref</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>底层 IMPLEMENTATION-DATA-TYPE 的路径，不是 SW-BASE-TYPE。</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>/AUTOSAR_Platform/ImplementationDataTypes/uint8</t>
         </is>
       </c>
     </row>
@@ -1892,230 +1860,230 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>枚举值对应文本；同一类型内不能重复。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Mode_Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Enumerations</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Implementation Data Type Ref</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>底层 IMPLEMENTATION-DATA-TYPE 的路径，不是 SW-BASE-TYPE。</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>/AUTOSAR_Platform/ImplementationDataTypes/uint8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Enumerations</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>Compu Method Ref</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>按 Type Path 推导</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>生成的计算方法路径；默认同级 CompuMethods 包中的同名对象。</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>/Pkg/CompuMethods/Mode</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Enumerations</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Data Constr Ref</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>按 Type Path 推导</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>生成的数据约束路径；默认同级 DataConstrs 包中的 dc_&lt;类型名&gt;。</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>/Pkg/DataConstrs/dc_Mode</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Enumerations</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Target ARXML</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>要插入对象的已有文件，相对 projectRoot；不是 outputDir 下的导出文件名。所在包也须已存在。</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>arxml/Types.arxml</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Arrays</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Arrays</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Type Path</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>新建实现数据类型的完整 AUTOSAR 路径；同路径的成员/枚举行按顺序合并。</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>/Pkg/Types/Mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Arrays</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Element Name</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>数组实现数据类型中的元素 SHORT-NAME。</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Arrays</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Element Type Ref</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>数组元素的实现数据类型路径。</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2132,7 +2100,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Array Size</t>
+          <t>Element Name</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2147,12 +2115,12 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>正整数；VARIABLE-SIZE 时表示声明的最大长度。</t>
+          <t>数组实现数据类型中的元素 SHORT-NAME。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2164,347 +2132,347 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
+          <t>Element Type Ref</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>数组元素的实现数据类型路径。</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>/Pkg/Types/Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Arrays</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Array Size</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>正整数；VARIABLE-SIZE 时表示声明的最大长度。</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Arrays</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
           <t>Array Size Semantics</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>FIXED-SIZE</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>数组大小语义。</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>FIXED-SIZE / VARIABLE-SIZE</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Arrays</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Target ARXML</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>要插入对象的已有文件，相对 projectRoot；不是 outputDir 下的导出文件名。所在包也须已存在。</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>arxml/Types.arxml</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="44" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Type Path</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>新建实现数据类型的完整 AUTOSAR 路径；同路径的成员/枚举行按顺序合并。</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>/Pkg/Types/Mode</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Member Name</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>一个成员一行；同一结构体成员名唯一，按行顺序生成。</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Member Type Ref</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>成员的实现数据类型路径，可引用本次新建的类型。</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>/Pkg/Types/Mode</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Target ARXML</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>要插入对象的已有文件，相对 projectRoot；不是 outputDir 下的导出文件名。所在包也须已存在。</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>arxml/Types.arxml</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>SR-Interfaces</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>SR-Interfaces</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Interface Path</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>新建接口的完整 AUTOSAR 路径；同路径的多行合并。</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>/Pkg/Interfaces/Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>SR-Interfaces</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Data Element Name</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>一个数据元素一行；同一接口内名称唯一。</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>State</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2484,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Data Type Ref</t>
+          <t>Interface Path</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>数据元素的实现数据类型路径。</t>
+          <t>新建接口的完整 AUTOSAR 路径；同路径的多行合并。</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>/Pkg/Types/Mode</t>
+          <t>/Pkg/Interfaces/Status</t>
         </is>
       </c>
     </row>
@@ -2548,27 +2516,27 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Is Queued</t>
+          <t>Data Element Name</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>可选</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Y 时生成 SW-IMPL-POLICY=QUEUED。</t>
+          <t>一个数据元素一行；同一接口内名称唯一。</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Y / N</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -2580,267 +2548,267 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
+          <t>Data Type Ref</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>数据元素的实现数据类型路径。</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>/Pkg/Types/Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>SR-Interfaces</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Is Queued</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Y 时生成 SW-IMPL-POLICY=QUEUED。</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Y / N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>SR-Interfaces</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
           <t>Is Service</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>接口级 IS-SERVICE；同一接口的所有行必须一致。</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Y / N</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="44" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>SR-Interfaces</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Target ARXML</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>要插入对象的已有文件，相对 projectRoot；不是 outputDir 下的导出文件名。所在包也须已存在。</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>arxml/Types.arxml</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>CS-Interfaces</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>CS-Interfaces</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Interface Path</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>新建接口的完整 AUTOSAR 路径；同路径的多行合并。</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>/Pkg/Interfaces/Status</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>CS-Interfaces</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Operation Name</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>一个参数一行；同一接口、同一 operation 的参数按行合并。无参数 operation 只填一行。</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>Reset / SetMode</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="44" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>CS-Interfaces</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Argument Name</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>有参数时必填</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>全空表示无参数</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>参数名、方向和类型必须全填或全空；同一 operation 不得混用无参数声明和参数行。</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>CS-Interfaces</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>有参数时必填</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>参数方向；与 Argument Name、Data Type Ref 一起填写。</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>IN / OUT / INOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>CS-Interfaces</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Data Type Ref</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>有参数时必填</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>参数的实现数据类型路径；无参数 operation 留空。</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>/Pkg/Types/Mode</t>
         </is>
       </c>
     </row>
@@ -2852,267 +2820,267 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>有参数时必填</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>参数方向；与 Argument Name、Data Type Ref 一起填写。</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>IN / OUT / INOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>CS-Interfaces</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Data Type Ref</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>有参数时必填</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>参数的实现数据类型路径；无参数 operation 留空。</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>/Pkg/Types/Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>CS-Interfaces</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>Is Service</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>接口级 IS-SERVICE；同一接口的所有行必须一致。</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>Y / N</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>CS-Interfaces</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Target ARXML</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>要插入对象的已有文件，相对 projectRoot；不是 outputDir 下的导出文件名。所在包也须已存在。</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>arxml/Types.arxml</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="36" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>P-Ports</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>P-Ports</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>SW-C</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>工作簿内组件标识；在 Components 中定义，不要求等于组件 SHORT-NAME。</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>LIT</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>P-Ports</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Port Name</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>端口 SHORT-NAME；同一组件内 P/R 两页之间也不能重名。</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>p_Status / r_Status</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>P-Ports</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Port Interface Ref</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>已有或本次新建接口的完整路径。</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>/Pkg/Interfaces/Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>P-Ports</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Create RTE Artifact</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Y：SR 按 Access Kind 创建全部元素的访问点；CS P 创建 runnable/event，CS R 创建同步调用点。不生成 C 源码。</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Y / N</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="44" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>P-Ports</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Runnable Name</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>SR 且 Artifact=Y 时必填</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>CS 自动命名</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>SR：已有 runnable 的简称。CS P：新建名称；留空用 RE_&lt;端口&gt;_&lt;operation&gt;，多 operation 时给手填名追加后缀。</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>Run / RE_Service</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3092,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Access Kind</t>
+          <t>Create RTE Artifact</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -3134,17 +3102,17 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>仅 SR 且 Artifact=Y 生效；Send 为显式发送，Write 为隐式写访问。</t>
+          <t>Y：SR 按 Access Kind 创建全部元素的访问点；CS P 创建 runnable/event，CS R 创建同步调用点。不生成 C 源码。</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Send / Write</t>
+          <t>Y / N</t>
         </is>
       </c>
     </row>
@@ -3156,59 +3124,59 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Transmission Acknowledge Timeout</t>
+          <t>Runnable Name</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
+          <t>SR 且 Artifact=Y 时必填</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>CS 自动命名</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>SR：已有 runnable 的简称。CS P：新建名称；留空用 RE_&lt;端口&gt;_&lt;operation&gt;，多 operation 时给手填名追加后缀。</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Run / RE_Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>P-Ports</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Access Kind</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>不生成</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>SR 发送确认超时，单位秒；非负数，填写 0 也会触发 ComSpec 生成。</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>P-Ports</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Uses End To End Protection</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>SR 发送端 E2E 标志；仅填 N 不会触发 ComSpec 生成。</t>
+          <t>仅 SR 且 Artifact=Y 生效；Send 为显式发送，Write 为隐式写访问。</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Y / N</t>
+          <t>Send / Write</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3188,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Runnable Symbol</t>
+          <t>Transmission Acknowledge Timeout</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -3230,17 +3198,17 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>与新建 runnable 名相同</t>
+          <t>不生成</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>仅 CS P 且 Artifact=Y 生效；C 函数符号，多 operation 时追加后缀。</t>
+          <t>SR 发送确认超时，单位秒；非负数，填写 0 也会触发 ComSpec 生成。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Service_Run</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
@@ -3252,235 +3220,235 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>Uses End To End Protection</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>SR 发送端 E2E 标志；仅填 N 不会触发 ComSpec 生成。</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Y / N</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>P-Ports</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Runnable Symbol</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>与新建 runnable 名相同</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>仅 CS P 且 Artifact=Y 生效；C 函数符号，多 operation 时追加后缀。</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Service_Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>P-Ports</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
           <t>Minimum Start Interval</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>0.0 秒</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>仅 CS P 且 Artifact=Y 生效；非负最小启动间隔，单位秒。</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>P-Ports</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Can Be Invoked Concurrently</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>仅 CS P 且 Artifact=Y 生效；允许并发调用。</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Y / N</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>R-Ports</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="44" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>R-Ports</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>SW-C</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>工作簿内组件标识；在 Components 中定义，不要求等于组件 SHORT-NAME。</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>LIT</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>R-Ports</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Port Name</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>端口 SHORT-NAME；同一组件内 P/R 两页之间也不能重名。</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>p_Status / r_Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>R-Ports</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Port Interface Ref</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>已有或本次新建接口的完整路径。</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>/Pkg/Interfaces/Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>R-Ports</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Create RTE Artifact</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Y：SR 按 Access Kind 创建全部元素的访问点；CS P 创建 runnable/event，CS R 创建同步调用点。不生成 C 源码。</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>Y / N</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3460,12 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Runnable Name</t>
+          <t>Port Interface Ref</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Artifact=Y 时必填</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -3507,12 +3475,12 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>组件内部行为中已有 runnable 的简称，不是完整 AUTOSAR 路径。</t>
+          <t>已有或本次新建接口的完整路径。</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>/Pkg/Interfaces/Status</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3492,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Access Kind</t>
+          <t>Create RTE Artifact</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3534,21 +3502,21 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>ReceiveByArgument</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>仅 SR 且 Artifact=Y 生效；ReceiveBy* 为显式接收，Read 为隐式读访问。也接受旧值 Argument / Value。</t>
+          <t>Y：SR 按 Access Kind 创建全部元素的访问点；CS P 创建 runnable/event，CS R 创建同步调用点。不生成 C 源码。</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>ReceiveByValue / Read</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="44" customHeight="1">
+          <t>Y / N</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
           <t>R-Ports</t>
@@ -3556,27 +3524,27 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Enable Update</t>
+          <t>Runnable Name</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>可选</t>
+          <t>Artifact=Y 时必填</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Y 时为全部 SR 数据元素创建非队列接收 ComSpec；与正数 Queue Length 互斥。</t>
+          <t>组件内部行为中已有 runnable 的简称，不是完整 AUTOSAR 路径。</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Y / N</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
@@ -3588,171 +3556,171 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
+          <t>Access Kind</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>ReceiveByArgument</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>仅 SR 且 Artifact=Y 生效；ReceiveBy* 为显式接收，Read 为隐式读访问。也接受旧值 Argument / Value。</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>ReceiveByValue / Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>R-Ports</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Enable Update</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Y 时为全部 SR 数据元素创建非队列接收 ComSpec；与正数 Queue Length 互斥。</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Y / N</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="44" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>R-Ports</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
           <t>Queue Length</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>0 / 不生成</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>非负整数；正数生成队列接收 ComSpec；0 或留空不生成，与 Enable Update=Y 互斥。</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Data Accesses</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>字段、必填条件、默认值、说明和示例如下。</t>
         </is>
       </c>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>必填条件</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>示例 / 取值</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="44" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>Data Accesses</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>SW-C</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>工作簿内组件标识；在 Components 中定义，不要求等于组件 SHORT-NAME。</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>LIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Data Accesses</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Runnable Name</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>已有 runnable 的简称；须已有对应访问点容器。</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>Data Accesses</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Port Name</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>已有或本次新建端口的 SHORT-NAME。</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>r_Status</t>
         </is>
       </c>
     </row>
@@ -3764,31 +3732,31 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Data Element Name</t>
+          <t>Runnable Name</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>多元素接口时必填</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>单元素自动选择</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>只处理指定的数据元素。</t>
+          <t>已有 runnable 的简称；须已有对应访问点容器。</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>State</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="44" customHeight="1">
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
           <t>Data Accesses</t>
@@ -3796,27 +3764,27 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Access Kind</t>
+          <t>Port Name</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>可选</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>P: Send / R: ReceiveByArgument</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>须匹配端口方向；本页可自定义名称或仅处理部分元素。</t>
+          <t>已有或本次新建端口的 SHORT-NAME。</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Send / ReceiveByArgument / ReceiveByValue / Read / Write</t>
+          <t>r_Status</t>
         </is>
       </c>
     </row>
@@ -3828,74 +3796,140 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
+          <t>Data Element Name</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>多元素接口时必填</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>单元素自动选择</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>只处理指定的数据元素。</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="44" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Data Accesses</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Access Kind</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>P: Send / R: ReceiveByArgument</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>须匹配端口方向；本页可自定义名称或仅处理部分元素。</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Send / ReceiveByArgument / ReceiveByValue / Read / Write</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Data Accesses</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
           <t>Access Name</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>按端口名自动生成</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>访问点 SHORT-NAME；同一 runnable 内不能冲突。</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>dra_Status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B92:F92"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B50:F50"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A23" location="'Components'!A1"/>
-    <hyperlink ref="A27" location="'Enumerations'!A1"/>
-    <hyperlink ref="A36" location="'Arrays'!A1"/>
-    <hyperlink ref="A44" location="'Structures'!A1"/>
-    <hyperlink ref="A50" location="'SR-Interfaces'!A1"/>
-    <hyperlink ref="A58" location="'CS-Interfaces'!A1"/>
-    <hyperlink ref="A67" location="'P-Ports'!A1"/>
-    <hyperlink ref="A80" location="'R-Ports'!A1"/>
-    <hyperlink ref="A90" location="'Data Accesses'!A1"/>
+    <hyperlink ref="A25" location="'Components'!A1"/>
+    <hyperlink ref="A29" location="'Enumerations'!A1"/>
+    <hyperlink ref="A38" location="'Arrays'!A1"/>
+    <hyperlink ref="A46" location="'Structures'!A1"/>
+    <hyperlink ref="A52" location="'SR-Interfaces'!A1"/>
+    <hyperlink ref="A60" location="'CS-Interfaces'!A1"/>
+    <hyperlink ref="A69" location="'P-Ports'!A1"/>
+    <hyperlink ref="A82" location="'R-Ports'!A1"/>
+    <hyperlink ref="A92" location="'Data Accesses'!A1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3971,7 +4005,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A90"/>
+    <hyperlink ref="A1" location="'README'!A92"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4015,7 +4049,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A23"/>
+    <hyperlink ref="A1" location="'README'!A25"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4099,7 +4133,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A27"/>
+    <hyperlink ref="A1" location="'README'!A29"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4179,7 +4213,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A36"/>
+    <hyperlink ref="A1" location="'README'!A38"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4237,7 +4271,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A44"/>
+    <hyperlink ref="A1" location="'README'!A46"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4317,7 +4351,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A50"/>
+    <hyperlink ref="A1" location="'README'!A52"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4404,7 +4438,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A58"/>
+    <hyperlink ref="A1" location="'README'!A60"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4534,7 +4568,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A67"/>
+    <hyperlink ref="A1" location="'README'!A69"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4637,7 +4671,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'README'!A80"/>
+    <hyperlink ref="A1" location="'README'!A82"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
